--- a/dist/figure_data/chuong3_phuong_phap_tables.xlsx
+++ b/dist/figure_data/chuong3_phuong_phap_tables.xlsx
@@ -15,7 +15,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="C35_Ký_hiệu_biến_tiếng_Việt" sheetId="6" state="visible" r:id="rId6"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="C36_Phân_tích_độ_vững_kiểm_t" sheetId="7" state="visible" r:id="rId7"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="C37_Bảng_định_nghĩa_biến_Ngh" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="C38_C38" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="C38_36_Tóm_tắt_phương_pháp_K" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -549,10 +549,14 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>C38_C38</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr"/>
+          <t>C38_36_Tóm_tắt_phương_pháp_K</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>3.6 Tóm tắt phương pháp: Kế thừa và đóng góp mới</t>
+        </is>
+      </c>
       <c r="C9" t="n">
         <v>11</v>
       </c>
